--- a/artfynd/A 62558-2023 artfynd.xlsx
+++ b/artfynd/A 62558-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62558-2023 artfynd.xlsx
+++ b/artfynd/A 62558-2023 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>53065781</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633915.7486155818</v>
+        <v>633916</v>
       </c>
       <c r="R5" t="n">
-        <v>6940275.359721025</v>
+        <v>6940275</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1127,19 +1127,9 @@
           <t>2013-06-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 62558-2023 artfynd.xlsx
+++ b/artfynd/A 62558-2023 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>53065781</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 62558-2023 artfynd.xlsx
+++ b/artfynd/A 62558-2023 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>53065781</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 62558-2023 artfynd.xlsx
+++ b/artfynd/A 62558-2023 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>53065781</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
